--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11B4DD4-D163-4F57-A61D-9C7DEE0C84CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB480538A9A1283EEF5E43466768DC5190" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A20AF813-2DB7-4508-9DB9-96CB76C6D8C6}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 09-09-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 14-09-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -416,9 +416,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,7 +432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -446,7 +446,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -460,7 +460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -474,7 +474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -488,7 +488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -502,7 +502,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -516,7 +516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -544,7 +544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>14</v>
       </c>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB480538A9A1283EEF5E43466768DC5190" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A20AF813-2DB7-4508-9DB9-96CB76C6D8C6}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48C5B4943D2832EF5E43466768DC5190" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1549359B-F4EB-4514-BB28-A49C33F0645A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48C5B4943D2832EF5E43466768DC5190" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1549359B-F4EB-4514-BB28-A49C33F0645A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF15A38-17D1-416C-A316-31FAF5560C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -416,9 +416,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,7 +432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -446,7 +446,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -460,7 +460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -474,7 +474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -488,7 +488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -502,7 +502,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -516,7 +516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -544,7 +544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF15A38-17D1-416C-A316-31FAF5560C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{903AC190-968F-4DD1-B9CA-7479013FCAA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 14-09-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 17-09-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -416,9 +416,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,7 +432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -446,7 +446,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -460,7 +460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -474,7 +474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -488,7 +488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -502,7 +502,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -516,7 +516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -544,7 +544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{903AC190-968F-4DD1-B9CA-7479013FCAA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7459423-8A37-4F27-87D5-74D3B77955A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7459423-8A37-4F27-87D5-74D3B77955A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48A5B38D856A3EEF5E43466768DC5190" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB3CD954-C50B-40C4-B4EA-8036A905AC88}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 17-09-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 21-09-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -416,9 +416,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,7 +432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -446,7 +446,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -460,7 +460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -474,7 +474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -488,7 +488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -502,7 +502,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -516,7 +516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -544,7 +544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>14</v>
       </c>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48A5B38D856A3EEF5E43466768DC5190" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB3CD954-C50B-40C4-B4EA-8036A905AC88}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F65ADE7F-C92C-48CB-8E20-26EB5FE918FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
@@ -416,9 +416,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,7 +432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -446,7 +446,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -460,7 +460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -474,7 +474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -488,7 +488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -502,7 +502,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -516,7 +516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -544,7 +544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F65ADE7F-C92C-48CB-8E20-26EB5FE918FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A4A7B0-C8C5-4C52-99B3-5D8E1C242CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 21-09-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 22-09-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A4A7B0-C8C5-4C52-99B3-5D8E1C242CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92EFD2D-EA3E-4895-B9F7-AD78141FB47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92EFD2D-EA3E-4895-B9F7-AD78141FB47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26049ED6-5C73-49CC-BC49-BC25D90CFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 22-09-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 23-09-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26049ED6-5C73-49CC-BC49-BC25D90CFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48453BC1852837EF5E43466768DC5190" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1D13162-6281-41B8-B4C1-862070205E8E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 23-09-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 24-09-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -416,9 +416,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,7 +432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -446,7 +446,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -460,7 +460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -474,7 +474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -488,7 +488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -502,7 +502,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -516,7 +516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -544,7 +544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>14</v>
       </c>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48453BC1852837EF5E43466768DC5190" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1D13162-6281-41B8-B4C1-862070205E8E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9789104-ABB8-44A4-A8CF-9852E7AFCB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 24-09-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 28-09-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -416,9 +416,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,7 +432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -446,7 +446,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -460,7 +460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -474,7 +474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -488,7 +488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -502,7 +502,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -516,7 +516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -544,7 +544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9789104-ABB8-44A4-A8CF-9852E7AFCB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48F5B7D80D882BEF5E43466768DC5190" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBA59A57-D435-4A35-878A-2E6F853C80CB}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 28-09-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 02-10-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -416,9 +416,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,7 +432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -446,7 +446,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -460,7 +460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -474,7 +474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -488,7 +488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -502,7 +502,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -516,7 +516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -544,7 +544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>14</v>
       </c>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92EFD2D-EA3E-4895-B9F7-AD78141FB47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A824100-0463-438E-BC20-35541E0C76BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 22-09-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 07-10-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48F5B7D80D882BEF5E43466768DC5190" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBA59A57-D435-4A35-878A-2E6F853C80CB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7096A46A-4973-4A9B-ACBC-11F68E9D9FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 02-10-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 07-10-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -416,9 +416,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,7 +432,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -446,7 +446,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -460,7 +460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -474,7 +474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -488,7 +488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -502,7 +502,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -516,7 +516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -544,7 +544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7096A46A-4973-4A9B-ACBC-11F68E9D9FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB483538B4052A33EF5E43466768DC5194" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF78D49C-37A0-431F-A439-12F7C85C08D6}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 07-10-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 08-10-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB483538B4052A33EF5E43466768DC5194" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF78D49C-37A0-431F-A439-12F7C85C08D6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920060A8-0199-4922-B588-7FAF072315A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 08-10-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 09-10-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920060A8-0199-4922-B588-7FAF072315A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6383E851-AF4D-4375-A7E8-3A008FB9F5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
+++ b/html/Telemedicinsk hjemmemonitoriering_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6383E851-AF4D-4375-A7E8-3A008FB9F5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48C5B3B3054A2FEF5E43466768DC5194" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0ACFF362-AD53-4F84-B57E-B6C785693B45}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 09-10-2026'!$A$1:$D$10</definedName>
+    <definedName name="Telemedicinsk_hjemmemonitoriering">'Opdateret d. 23-10-2026'!$A$1:$D$10</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
